--- a/sheets/대금율보/검수/사모곡.xlsx
+++ b/sheets/대금율보/검수/사모곡.xlsx
@@ -5460,7 +5460,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
-–南‹</t>
+–南</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -5471,7 +5471,7 @@
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林
-–林‹</t>
+–林</t>
         </is>
       </c>
       <c r="G3" s="22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-汰無‹</t>
+汰無</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -5591,7 +5591,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無
-無無)‹</t>
+無無)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -6015,7 +6015,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無
-無無‹</t>
+無無</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="J20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
@@ -6420,7 +6420,7 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-汰無‹</t>
+汰無</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">

--- a/sheets/대금율보/검수/사모곡.xlsx
+++ b/sheets/대금율보/검수/사모곡.xlsx
@@ -5408,24 +5408,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="100.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="74.58" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="74.58" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="74.58" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="74.58" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="74.58" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="74.58" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="74.58" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="74.58" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="74.58" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="74.58" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="74.58" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="74.58" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="74.58" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="74.58" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="74.58" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="74.58" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="M18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="74.58" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="74.58" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="M20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="74.58" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="M21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="74.58" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="M22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="74.58" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="74.58" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="M24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="74.58" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="M25" s="23"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="74.58" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="24"/>
@@ -6678,6 +6678,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="40"/>
 </worksheet>
 </file>